--- a/Fase 1/Evidencias Grupales/05 plantilla_sprint_backlog_actividades_horas.xlsx
+++ b/Fase 1/Evidencias Grupales/05 plantilla_sprint_backlog_actividades_horas.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
   <si>
     <t xml:space="preserve">Resultado de la actividad Sprint Planning </t>
   </si>
@@ -41,112 +41,223 @@
     <t>Horas estimadas</t>
   </si>
   <si>
-    <t>001D</t>
-  </si>
-  <si>
-    <t>Creación de registro</t>
-  </si>
-  <si>
-    <t>002D</t>
-  </si>
-  <si>
-    <t>Creación de login</t>
-  </si>
-  <si>
-    <t>003D</t>
-  </si>
-  <si>
-    <t>Creación vista usuario base</t>
-  </si>
-  <si>
-    <t>004D</t>
-  </si>
-  <si>
-    <t>Creacion formulario ticket</t>
-  </si>
-  <si>
-    <t>005D</t>
-  </si>
-  <si>
-    <t>Creación base de datos</t>
-  </si>
-  <si>
-    <t>006D</t>
-  </si>
-  <si>
-    <t>Creación vista depto. seguridad</t>
-  </si>
-  <si>
-    <t>007D</t>
-  </si>
-  <si>
-    <t>Creación vista depto. mantención</t>
+    <t>HU-01</t>
+  </si>
+  <si>
+    <t>Iniciar sesión</t>
+  </si>
+  <si>
+    <t>Diseñar interfaz de login</t>
+  </si>
+  <si>
+    <t>Implementar autenticación de usuario</t>
+  </si>
+  <si>
+    <t>Validar credenciales en backend</t>
+  </si>
+  <si>
+    <t>HU-02</t>
+  </si>
+  <si>
+    <t>Cerrar sesión</t>
+  </si>
+  <si>
+    <t>Implementar botón de cierre de sesión</t>
+  </si>
+  <si>
+    <t>Manejar destrucción de sesión</t>
+  </si>
+  <si>
+    <t>HU-03</t>
+  </si>
+  <si>
+    <t>Control de acceso por rol</t>
+  </si>
+  <si>
+    <t>Diseñar roles de usuario</t>
+  </si>
+  <si>
+    <t>Implementar permisos en el sistema</t>
+  </si>
+  <si>
+    <t>HU-04</t>
+  </si>
+  <si>
+    <t>Crear ticket</t>
+  </si>
+  <si>
+    <t>Diseñar formulario de creación de ticket</t>
+  </si>
+  <si>
+    <t>Implementar lógica para guardar ticket</t>
+  </si>
+  <si>
+    <t>HU-05</t>
+  </si>
+  <si>
+    <t>Cancelar ticket</t>
+  </si>
+  <si>
+    <t>Implementar cancelación de ticket</t>
+  </si>
+  <si>
+    <t>HU-06</t>
+  </si>
+  <si>
+    <t>Cambiar estado ticket</t>
+  </si>
+  <si>
+    <t>Implementar cambio de estado</t>
   </si>
   <si>
     <t>Sprint Backlog con estimación de tareas para las historia de usuario del Segundo Sprint</t>
   </si>
   <si>
-    <t>008D</t>
-  </si>
-  <si>
-    <t>Implementar gestion de ticket en depto. seguridad</t>
-  </si>
-  <si>
-    <t>009D</t>
-  </si>
-  <si>
-    <t>Implementar gestion de ticket en depto. mantención</t>
-  </si>
-  <si>
-    <t>010D</t>
-  </si>
-  <si>
-    <t>Implementar limitaciones del ticket</t>
-  </si>
-  <si>
-    <t>011D</t>
-  </si>
-  <si>
-    <t>Implementar gestion entre departamentos</t>
-  </si>
-  <si>
-    <t>012D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implementar asignacion de trabajadores en deto. seguridad </t>
-  </si>
-  <si>
-    <t>013D</t>
-  </si>
-  <si>
-    <t>Implementar asignacion de trabajadores en deto. mantención</t>
-  </si>
-  <si>
-    <t>014D</t>
-  </si>
-  <si>
-    <t>Creación historial de tickets</t>
+    <t>HU-07</t>
+  </si>
+  <si>
+    <t>Gestionar tickets</t>
+  </si>
+  <si>
+    <t>Crear vista de listado de tickets</t>
+  </si>
+  <si>
+    <t>Implementar filtros y ordenamiento</t>
+  </si>
+  <si>
+    <t>HU-08</t>
+  </si>
+  <si>
+    <t>Cerrar ticket</t>
+  </si>
+  <si>
+    <t>Implementar función de cierre de ticket</t>
+  </si>
+  <si>
+    <t>HU-11</t>
+  </si>
+  <si>
+    <t>Asignar tickets</t>
+  </si>
+  <si>
+    <t>Diseñar interfaz de asignación</t>
+  </si>
+  <si>
+    <t>Implementar asignación a agentes</t>
+  </si>
+  <si>
+    <t>HU-12</t>
+  </si>
+  <si>
+    <t>Escalar casos complejos</t>
+  </si>
+  <si>
+    <t>Implementar lógica de escalamiento</t>
+  </si>
+  <si>
+    <t>HU-13</t>
+  </si>
+  <si>
+    <t>Balancear carga</t>
+  </si>
+  <si>
+    <t>Crear lógica de distribución de tickets</t>
+  </si>
+  <si>
+    <t>HU-17</t>
+  </si>
+  <si>
+    <t>Reasignar tickets</t>
+  </si>
+  <si>
+    <t>Implementar cambio de responsable</t>
   </si>
   <si>
     <t>Sprint Backlog con estimación de tareas para las historia de usuario del Tercer Sprint</t>
   </si>
   <si>
-    <t>015D</t>
-  </si>
-  <si>
-    <t>Implementar re-asignacion de trabajadores en depto. mantencion</t>
-  </si>
-  <si>
-    <t>016D</t>
-  </si>
-  <si>
-    <t>Implementar escalamiento de ticket</t>
-  </si>
-  <si>
-    <t>017D</t>
-  </si>
-  <si>
-    <t>Montaje final (Un poco de todo)</t>
+    <t>HU-09</t>
+  </si>
+  <si>
+    <t>Medir eficiencia</t>
+  </si>
+  <si>
+    <t>Diseñar métricas de desempeño</t>
+  </si>
+  <si>
+    <t>Implementar cálculo de métricas</t>
+  </si>
+  <si>
+    <t>HU-10</t>
+  </si>
+  <si>
+    <t>Trazabilidad de tickets</t>
+  </si>
+  <si>
+    <t>Implementar registro de cambios</t>
+  </si>
+  <si>
+    <t>HU-14</t>
+  </si>
+  <si>
+    <t>Seguimiento de incidentes</t>
+  </si>
+  <si>
+    <t>Crear vista de seguimiento</t>
+  </si>
+  <si>
+    <t>HU-15</t>
+  </si>
+  <si>
+    <t>Historial de tickets</t>
+  </si>
+  <si>
+    <t>Implementar historial de acciones</t>
+  </si>
+  <si>
+    <t>HU-16</t>
+  </si>
+  <si>
+    <t>Organizar trabajo</t>
+  </si>
+  <si>
+    <t>Crear panel de tareas pendientes</t>
+  </si>
+  <si>
+    <t>HU-18</t>
+  </si>
+  <si>
+    <t>Buscar información</t>
+  </si>
+  <si>
+    <t>Implementar buscador de tickets</t>
+  </si>
+  <si>
+    <t>HU-19</t>
+  </si>
+  <si>
+    <t>Gestionar urgencias</t>
+  </si>
+  <si>
+    <t>Implementar prioridad de tickets</t>
+  </si>
+  <si>
+    <t>HU-20</t>
+  </si>
+  <si>
+    <t>Adaptarse a cambios</t>
+  </si>
+  <si>
+    <t>Permitir modificación de tickets</t>
+  </si>
+  <si>
+    <t>HU-21</t>
+  </si>
+  <si>
+    <t>Generar información para decisiones</t>
+  </si>
+  <si>
+    <t>Crear reportes del sistema</t>
   </si>
 </sst>
 </file>
@@ -227,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -253,20 +364,17 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -518,7 +626,7 @@
       <c r="B4" s="3"/>
       <c r="C4" s="4">
         <f>SUM(D7:D80)</f>
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
@@ -541,219 +649,251 @@
       <c r="A7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="9">
-        <v>1.0</v>
+      <c r="B7" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="9">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="8" ht="38.25" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="9">
-        <v>2.0</v>
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>8</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="9">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="9" ht="38.25" customHeight="1">
       <c r="A9" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="9">
-        <v>3.0</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>12</v>
-      </c>
       <c r="D9" s="9">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="10" ht="38.25" customHeight="1">
       <c r="A10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B10" s="9" t="s">
         <v>13</v>
-      </c>
-      <c r="B10" s="9">
-        <v>4.0</v>
       </c>
       <c r="C10" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="9">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="11" ht="38.25" customHeight="1">
       <c r="A11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="9">
-        <v>5.0</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>16</v>
-      </c>
       <c r="D11" s="9">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="12" ht="38.25" customHeight="1">
       <c r="A12" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="9" t="s">
         <v>17</v>
-      </c>
-      <c r="B12" s="9">
-        <v>6.0</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D12" s="9">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="13" ht="38.25" customHeight="1">
       <c r="A13" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="9">
-        <v>7.0</v>
-      </c>
-      <c r="C13" s="9" t="s">
+      <c r="D13" s="9">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="14" ht="38.25" customHeight="1">
+      <c r="A14" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="9">
+      <c r="B14" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="9">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="15" ht="38.25" customHeight="1">
+      <c r="A15" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" s="9">
         <v>6.0</v>
       </c>
     </row>
-    <row r="14" ht="38.25" customHeight="1">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
-    </row>
-    <row r="15" ht="38.25" customHeight="1">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="11"/>
-    </row>
     <row r="16" ht="38.25" customHeight="1">
-      <c r="A16" s="9"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="11"/>
+      <c r="A16" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D16" s="9">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="17" ht="38.25" customHeight="1">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+      <c r="A17" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="9">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="18" ht="38.25" customHeight="1">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" ht="38.25" customHeight="1">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
     </row>
     <row r="20" ht="38.25" customHeight="1">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" ht="38.25" customHeight="1">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" ht="38.25" customHeight="1">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
     </row>
     <row r="23" ht="38.25" customHeight="1">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" ht="38.25" customHeight="1">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
     </row>
     <row r="25" ht="38.25" customHeight="1">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
     </row>
     <row r="26" ht="38.25" customHeight="1">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
     </row>
     <row r="27" ht="38.25" customHeight="1">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
     </row>
     <row r="28" ht="38.25" customHeight="1">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="C29" s="12"/>
+      <c r="C29" s="11"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
-      <c r="C30" s="12"/>
+      <c r="C30" s="11"/>
     </row>
     <row r="31" ht="14.25" customHeight="1">
-      <c r="C31" s="12"/>
+      <c r="C31" s="11"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="C32" s="12"/>
+      <c r="C32" s="11"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="C33" s="12"/>
+      <c r="C33" s="11"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="C34" s="12"/>
+      <c r="C34" s="11"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
-      <c r="C35" s="12"/>
+      <c r="C35" s="11"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
-      <c r="C36" s="12"/>
+      <c r="C36" s="11"/>
     </row>
     <row r="37" ht="14.25" customHeight="1">
-      <c r="C37" s="12"/>
+      <c r="C37" s="11"/>
     </row>
     <row r="38" ht="14.25" customHeight="1">
-      <c r="C38" s="12"/>
+      <c r="C38" s="11"/>
     </row>
     <row r="39" ht="14.25" customHeight="1"/>
     <row r="40" ht="14.25" customHeight="1"/>
@@ -1744,8 +1884,8 @@
       <c r="B1" s="1"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="s">
-        <v>21</v>
+      <c r="A2" s="12" t="s">
+        <v>30</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -1760,7 +1900,7 @@
       <c r="B4" s="3"/>
       <c r="C4" s="4">
         <f>SUM(D7:D80)</f>
-        <v>48</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" ht="41.25" customHeight="1">
@@ -1779,190 +1919,199 @@
     </row>
     <row r="7" ht="38.25" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="9">
-        <v>8.0</v>
+        <v>31</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D7" s="9">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="8" ht="38.25" customHeight="1">
       <c r="A8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="9">
-        <v>9.0</v>
+        <v>31</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>32</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D8" s="9">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="9" ht="38.25" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="9">
-        <v>10.0</v>
+        <v>35</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>36</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D9" s="9">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="10" ht="38.25" customHeight="1">
       <c r="A10" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B10" s="9">
-        <v>11.0</v>
+        <v>38</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D10" s="9">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="11" ht="38.25" customHeight="1">
       <c r="A11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="9">
-        <v>12.0</v>
+        <v>38</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D11" s="9">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="12" ht="38.25" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="9">
-        <v>13.0</v>
+        <v>42</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>43</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D12" s="9">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="13" ht="38.25" customHeight="1">
       <c r="A13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="9">
-        <v>14.0</v>
+        <v>45</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D13" s="9">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="14" ht="38.25" customHeight="1">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="D14" s="11"/>
+      <c r="A14" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="9">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="15" ht="38.25" customHeight="1">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="A15" s="10"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
     </row>
     <row r="16" ht="38.25" customHeight="1">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="A16" s="10"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
     </row>
     <row r="17" ht="38.25" customHeight="1">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
     </row>
     <row r="18" ht="38.25" customHeight="1">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" ht="38.25" customHeight="1">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
     </row>
     <row r="20" ht="38.25" customHeight="1">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" ht="38.25" customHeight="1">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" ht="38.25" customHeight="1">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
     </row>
     <row r="23" ht="38.25" customHeight="1">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" ht="38.25" customHeight="1">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
     </row>
     <row r="25" ht="38.25" customHeight="1">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
     </row>
     <row r="26" ht="38.25" customHeight="1">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
     </row>
     <row r="27" ht="38.25" customHeight="1">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
     </row>
     <row r="28" ht="38.25" customHeight="1">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1988,8 +2137,8 @@
       <c r="B1" s="1"/>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="s">
-        <v>36</v>
+      <c r="A2" s="12" t="s">
+        <v>51</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -2004,7 +2153,7 @@
       <c r="B4" s="3"/>
       <c r="C4" s="4">
         <f>SUM(D7:D80)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" ht="41.25" customHeight="1">
@@ -2023,159 +2172,215 @@
     </row>
     <row r="7" ht="38.25" customHeight="1">
       <c r="A7" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="14">
-        <v>15.0</v>
+        <v>52</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D7" s="9">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="8" ht="38.25" customHeight="1">
       <c r="A8" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="14">
-        <v>16.0</v>
+        <v>52</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>53</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="D8" s="9">
-        <v>8.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="9" ht="38.25" customHeight="1">
       <c r="A9" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="14">
-        <v>17.0</v>
+        <v>56</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>57</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="D9" s="9">
-        <v>24.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="10" ht="38.25" customHeight="1">
-      <c r="A10" s="14"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="11"/>
+      <c r="A10" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="9">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="11" ht="38.25" customHeight="1">
-      <c r="A11" s="14"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="11"/>
+      <c r="A11" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="9">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="12" ht="38.25" customHeight="1">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="11"/>
+      <c r="A12" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="9">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="13" ht="38.25" customHeight="1">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="11"/>
+      <c r="A13" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="9">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="14" ht="38.25" customHeight="1">
-      <c r="A14" s="15"/>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="11"/>
+      <c r="A14" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" s="9">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="15" ht="38.25" customHeight="1">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
+      <c r="A15" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" s="9">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="16" ht="38.25" customHeight="1">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
+      <c r="A16" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D16" s="9">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="17" ht="38.25" customHeight="1">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
     </row>
     <row r="18" ht="38.25" customHeight="1">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
     </row>
     <row r="19" ht="38.25" customHeight="1">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
     </row>
     <row r="20" ht="38.25" customHeight="1">
-      <c r="A20" s="11"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
     </row>
     <row r="21" ht="38.25" customHeight="1">
-      <c r="A21" s="11"/>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
     </row>
     <row r="22" ht="38.25" customHeight="1">
-      <c r="A22" s="11"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
     </row>
     <row r="23" ht="38.25" customHeight="1">
-      <c r="A23" s="11"/>
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
     </row>
     <row r="24" ht="38.25" customHeight="1">
-      <c r="A24" s="11"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
     </row>
     <row r="25" ht="38.25" customHeight="1">
-      <c r="A25" s="11"/>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
     </row>
     <row r="26" ht="38.25" customHeight="1">
-      <c r="A26" s="11"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
     </row>
     <row r="27" ht="38.25" customHeight="1">
-      <c r="A27" s="11"/>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
     </row>
     <row r="28" ht="38.25" customHeight="1">
-      <c r="A28" s="11"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
